--- a/results/Int Task Remove ACC 0.3/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC 0.3/Rando_10_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6222572593270908</v>
+        <v>0.6243287153280359</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6280410894160044</v>
+        <v>0.6246868815171477</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6276829232268928</v>
+        <v>0.6236559536820961</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6361312143680028</v>
+        <v>0.6214271999527368</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6384375092310873</v>
+        <v>0.6176882403332054</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6389529731486132</v>
+        <v>0.6176882403332054</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6405163501019111</v>
+        <v>0.6185788556405636</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6401146131805158</v>
+        <v>0.6240480902726494</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6441947537884383</v>
+        <v>0.623147874634449</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.646614775647653</v>
+        <v>0.6214877558857412</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6486330605854724</v>
+        <v>0.6217321950787227</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6491485245029982</v>
+        <v>0.6217321950787227</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6486840161876348</v>
+        <v>0.6158176527929577</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6480814108055416</v>
+        <v>0.6180537913921957</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6384692641715652</v>
+        <v>0.6095109739166396</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6353764806664106</v>
+        <v>0.6048186275957818</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6345464212920569</v>
+        <v>0.5967189023129412</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6345464212920569</v>
+        <v>0.6039353971583021</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.62670073553304</v>
+        <v>0.588512834903849</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6250406167843323</v>
+        <v>0.5926195610433345</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6250406167843323</v>
+        <v>0.6019584674918028</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6282035565533335</v>
+        <v>0.5912910229521755</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6272863557144124</v>
+        <v>0.5960874959383216</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6272863557144124</v>
+        <v>0.547648657430656</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6173086580214457</v>
+        <v>0.4846483324963814</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.618383156588781</v>
+        <v>0.4915502318849142</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6152903730836263</v>
+        <v>0.4982150769503441</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5937376303429533</v>
+        <v>0.4965815437331994</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5904609635778217</v>
+        <v>0.4993405311198417</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.595240451363247</v>
+        <v>0.4913035772309692</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5966561309189732</v>
+        <v>0.4897402002776711</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5994247186364576</v>
+        <v>0.4875912031430006</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5824675804212329</v>
+        <v>0.4679769887454583</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5802654122234366</v>
+        <v>0.4674615248279326</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5764828818716214</v>
+        <v>0.4649277759725874</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5650895046229285</v>
+        <v>0.4823250524325761</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5650023631583612</v>
+        <v>0.4853041089416004</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5650023631583612</v>
+        <v>0.48810888252149</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5860854281747556</v>
+        <v>0.4959523528195433</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5766763654624405</v>
+        <v>0.4988878385962839</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5747282367884679</v>
+        <v>0.4876613594068473</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6028032966059138</v>
+        <v>0.4843750923108735</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5738863616223082</v>
+        <v>0.4391715652970195</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.574271113342983</v>
+        <v>0.4348617552358728</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5672746876200041</v>
+        <v>0.4333419490148584</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5624538445632588</v>
+        <v>0.4628208725962248</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5493250228930966</v>
+        <v>0.4902859421616991</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5489698106519363</v>
+        <v>0.4910022745399226</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5497437450152127</v>
+        <v>0.4955011372699613</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5419172599178803</v>
+        <v>0.4947412341594541</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5495406610935516</v>
+        <v>0.4950994003485659</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5420701267243671</v>
+        <v>0.4953002688092636</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5501336661448025</v>
+        <v>0.4642535373526718</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5441415827253124</v>
+        <v>0.4455853247865773</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5504918323339143</v>
+        <v>0.4244099488967004</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5423477978318022</v>
+        <v>0.419736803237527</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5645489321478155</v>
+        <v>0.4308399550999912</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5567564174519245</v>
+        <v>0.4315562874782147</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.542333028092045</v>
+        <v>0.4886620092753966</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.479759548636753</v>
+        <v>0.4886620092753966</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4795320946444923</v>
+        <v>0.4883038430862848</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4789560747939621</v>
+        <v>0.49062712315009</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4825185360233953</v>
+        <v>0.4921469293711045</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4622751307121968</v>
+        <v>0.4873600567158006</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4672724721590406</v>
+        <v>0.4893251705904942</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4766985200720764</v>
+        <v>0.490155229964848</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4766985200720764</v>
+        <v>0.4940950580450773</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4766985200720764</v>
+        <v>0.4910990163353322</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4761830561545506</v>
+        <v>0.49062712315009</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4833493338847369</v>
+        <v>0.4979913153930228</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4843366909875048</v>
+        <v>0.475414291200189</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4770766254098603</v>
+        <v>0.4818516822733583</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4868512391811657</v>
+        <v>0.4818516822733583</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4857767406138304</v>
+        <v>0.4878533660236907</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4801406079224884</v>
+        <v>0.4967085634951112</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4765493457005288</v>
+        <v>0.5011468702921454</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4722269813605884</v>
+        <v>0.4967373644876377</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5016697190795498</v>
+        <v>0.4967373644876377</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4999394440669955</v>
+        <v>0.506308155850294</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5002976102561073</v>
+        <v>0.5060711015271911</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4981751986529998</v>
+        <v>0.5051081144950226</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4970135586210971</v>
+        <v>0.4946924940182554</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4952397128762591</v>
+        <v>0.4911544028594216</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4999564292677163</v>
+        <v>0.4909971051310076</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4999564292677163</v>
+        <v>0.4835214013529081</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4985237645112693</v>
+        <v>0.4835361710926653</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4990392284287951</v>
+        <v>0.4985237645112693</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4990392284287951</v>
+        <v>0.4997991315393023</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.498724632971967</v>
+        <v>0.5004718931852421</v>
       </c>
     </row>
   </sheetData>
